--- a/templates/Templates_HO.xlsx
+++ b/templates/Templates_HO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aletheia/Desktop/Paediatrics/Admin/RosterApp/HO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aletheia/Desktop/Paediatrics/Admin/RosterApp/roster/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F7E4F7-5E6A-A445-919A-288732CBCA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8155D6-C2F1-4944-A72D-E8A69C7EAB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1820" yWindow="1280" windowWidth="19900" windowHeight="16600" activeTab="2" xr2:uid="{B6EBF472-D0B5-0C4E-A945-41133059122F}"/>
+    <workbookView xWindow="0" yWindow="1280" windowWidth="19900" windowHeight="16600" activeTab="2" xr2:uid="{B6EBF472-D0B5-0C4E-A945-41133059122F}"/>
   </bookViews>
   <sheets>
     <sheet name="Lookup Data" sheetId="7" state="hidden" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3198" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3197" uniqueCount="288">
   <si>
     <t>Old cycle</t>
   </si>
@@ -3483,7 +3483,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3499,15 +3511,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="56" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3595,9 +3598,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="39" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4549,12 +4549,12 @@
       <c r="AN3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="AP3" s="429" t="s">
+      <c r="AP3" s="430" t="s">
         <v>120</v>
       </c>
-      <c r="AQ3" s="429"/>
-      <c r="AR3" s="429"/>
-      <c r="AS3" s="429"/>
+      <c r="AQ3" s="430"/>
+      <c r="AR3" s="430"/>
+      <c r="AS3" s="430"/>
     </row>
     <row r="4" spans="2:73" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F4" s="1" t="s">
@@ -4563,30 +4563,30 @@
       <c r="H4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AP4" s="411" t="s">
+      <c r="AP4" s="412" t="s">
         <v>133</v>
       </c>
-      <c r="AQ4" s="412"/>
-      <c r="AR4" s="412"/>
-      <c r="AS4" s="413"/>
-      <c r="AT4" s="414" t="s">
+      <c r="AQ4" s="413"/>
+      <c r="AR4" s="413"/>
+      <c r="AS4" s="414"/>
+      <c r="AT4" s="415" t="s">
         <v>175</v>
       </c>
-      <c r="AU4" s="415"/>
-      <c r="AV4" s="415"/>
-      <c r="AW4" s="415"/>
-      <c r="AX4" s="415"/>
-      <c r="AY4" s="415"/>
-      <c r="AZ4" s="415"/>
-      <c r="BA4" s="415"/>
-      <c r="BB4" s="415"/>
-      <c r="BC4" s="415"/>
-      <c r="BD4" s="415"/>
-      <c r="BE4" s="415"/>
-      <c r="BF4" s="415"/>
-      <c r="BG4" s="415"/>
-      <c r="BH4" s="415"/>
-      <c r="BI4" s="416"/>
+      <c r="AU4" s="416"/>
+      <c r="AV4" s="416"/>
+      <c r="AW4" s="416"/>
+      <c r="AX4" s="416"/>
+      <c r="AY4" s="416"/>
+      <c r="AZ4" s="416"/>
+      <c r="BA4" s="416"/>
+      <c r="BB4" s="416"/>
+      <c r="BC4" s="416"/>
+      <c r="BD4" s="416"/>
+      <c r="BE4" s="416"/>
+      <c r="BF4" s="416"/>
+      <c r="BG4" s="416"/>
+      <c r="BH4" s="416"/>
+      <c r="BI4" s="417"/>
     </row>
     <row r="5" spans="2:73" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
@@ -4732,34 +4732,34 @@
         <v>45936</v>
       </c>
       <c r="AO5" s="5"/>
-      <c r="AP5" s="417" t="s">
+      <c r="AP5" s="418" t="s">
         <v>170</v>
       </c>
-      <c r="AQ5" s="418"/>
-      <c r="AR5" s="418"/>
-      <c r="AS5" s="419"/>
-      <c r="AT5" s="423" t="s">
+      <c r="AQ5" s="419"/>
+      <c r="AR5" s="419"/>
+      <c r="AS5" s="420"/>
+      <c r="AT5" s="424" t="s">
         <v>176</v>
       </c>
-      <c r="AU5" s="424"/>
-      <c r="AV5" s="424"/>
-      <c r="AW5" s="424"/>
-      <c r="AX5" s="424"/>
-      <c r="AY5" s="425"/>
-      <c r="AZ5" s="423" t="s">
+      <c r="AU5" s="425"/>
+      <c r="AV5" s="425"/>
+      <c r="AW5" s="425"/>
+      <c r="AX5" s="425"/>
+      <c r="AY5" s="426"/>
+      <c r="AZ5" s="424" t="s">
         <v>188</v>
       </c>
-      <c r="BA5" s="424"/>
-      <c r="BB5" s="424"/>
-      <c r="BC5" s="424"/>
-      <c r="BD5" s="425"/>
-      <c r="BE5" s="423" t="s">
+      <c r="BA5" s="425"/>
+      <c r="BB5" s="425"/>
+      <c r="BC5" s="425"/>
+      <c r="BD5" s="426"/>
+      <c r="BE5" s="424" t="s">
         <v>170</v>
       </c>
-      <c r="BF5" s="424"/>
-      <c r="BG5" s="424"/>
-      <c r="BH5" s="424"/>
-      <c r="BI5" s="425"/>
+      <c r="BF5" s="425"/>
+      <c r="BG5" s="425"/>
+      <c r="BH5" s="425"/>
+      <c r="BI5" s="426"/>
       <c r="BJ5" s="5"/>
       <c r="BK5" s="5"/>
       <c r="BL5" s="5"/>
@@ -4919,26 +4919,26 @@
         <v>1</v>
       </c>
       <c r="AO6" s="5"/>
-      <c r="AP6" s="420"/>
-      <c r="AQ6" s="421"/>
-      <c r="AR6" s="421"/>
-      <c r="AS6" s="422"/>
-      <c r="AT6" s="426"/>
-      <c r="AU6" s="427"/>
-      <c r="AV6" s="427"/>
-      <c r="AW6" s="427"/>
-      <c r="AX6" s="427"/>
-      <c r="AY6" s="428"/>
-      <c r="AZ6" s="426"/>
-      <c r="BA6" s="427"/>
-      <c r="BB6" s="427"/>
-      <c r="BC6" s="427"/>
-      <c r="BD6" s="428"/>
-      <c r="BE6" s="426"/>
-      <c r="BF6" s="427"/>
-      <c r="BG6" s="427"/>
-      <c r="BH6" s="427"/>
-      <c r="BI6" s="428"/>
+      <c r="AP6" s="421"/>
+      <c r="AQ6" s="422"/>
+      <c r="AR6" s="422"/>
+      <c r="AS6" s="423"/>
+      <c r="AT6" s="427"/>
+      <c r="AU6" s="428"/>
+      <c r="AV6" s="428"/>
+      <c r="AW6" s="428"/>
+      <c r="AX6" s="428"/>
+      <c r="AY6" s="429"/>
+      <c r="AZ6" s="427"/>
+      <c r="BA6" s="428"/>
+      <c r="BB6" s="428"/>
+      <c r="BC6" s="428"/>
+      <c r="BD6" s="429"/>
+      <c r="BE6" s="427"/>
+      <c r="BF6" s="428"/>
+      <c r="BG6" s="428"/>
+      <c r="BH6" s="428"/>
+      <c r="BI6" s="429"/>
       <c r="BJ6" s="5"/>
       <c r="BK6" s="5"/>
       <c r="BL6" s="5"/>
@@ -12147,12 +12147,12 @@
       <c r="AX3" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="BD3" s="430" t="s">
+      <c r="BD3" s="431" t="s">
         <v>88</v>
       </c>
-      <c r="BE3" s="430"/>
-      <c r="BF3" s="430"/>
-      <c r="BG3" s="430"/>
+      <c r="BE3" s="431"/>
+      <c r="BF3" s="431"/>
+      <c r="BG3" s="431"/>
       <c r="BM3" s="99" t="s">
         <v>120</v>
       </c>
@@ -19600,9 +19600,9 @@
       <c r="AO1" s="355"/>
       <c r="AP1" s="355"/>
       <c r="AQ1" s="355"/>
-      <c r="AS1" s="393"/>
-      <c r="AT1" s="393"/>
-      <c r="AU1" s="393"/>
+      <c r="AS1" s="394"/>
+      <c r="AT1" s="394"/>
+      <c r="AU1" s="394"/>
       <c r="AV1" s="352"/>
     </row>
     <row r="2" spans="2:72" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -19815,28 +19815,28 @@
       <c r="AO3" s="355"/>
       <c r="AP3" s="355"/>
       <c r="AQ3" s="355"/>
-      <c r="AS3" s="396" t="s">
+      <c r="AS3" s="400" t="s">
         <v>268</v>
       </c>
-      <c r="AT3" s="397"/>
-      <c r="AU3" s="397"/>
-      <c r="AV3" s="398"/>
-      <c r="AW3" s="396" t="s">
+      <c r="AT3" s="401"/>
+      <c r="AU3" s="401"/>
+      <c r="AV3" s="402"/>
+      <c r="AW3" s="400" t="s">
         <v>175</v>
       </c>
-      <c r="AX3" s="397"/>
-      <c r="AY3" s="397"/>
-      <c r="AZ3" s="397"/>
-      <c r="BA3" s="397"/>
-      <c r="BB3" s="397"/>
-      <c r="BC3" s="397"/>
-      <c r="BD3" s="397"/>
-      <c r="BE3" s="397"/>
-      <c r="BF3" s="397"/>
-      <c r="BG3" s="397"/>
-      <c r="BH3" s="397"/>
-      <c r="BI3" s="397"/>
-      <c r="BJ3" s="398"/>
+      <c r="AX3" s="401"/>
+      <c r="AY3" s="401"/>
+      <c r="AZ3" s="401"/>
+      <c r="BA3" s="401"/>
+      <c r="BB3" s="401"/>
+      <c r="BC3" s="401"/>
+      <c r="BD3" s="401"/>
+      <c r="BE3" s="401"/>
+      <c r="BF3" s="401"/>
+      <c r="BG3" s="401"/>
+      <c r="BH3" s="401"/>
+      <c r="BI3" s="401"/>
+      <c r="BJ3" s="402"/>
     </row>
     <row r="4" spans="2:72" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G4" s="1" t="s">
@@ -19845,32 +19845,32 @@
       <c r="I4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AS4" s="399" t="s">
+      <c r="AS4" s="395" t="s">
         <v>170</v>
       </c>
-      <c r="AT4" s="400"/>
-      <c r="AU4" s="400"/>
-      <c r="AV4" s="401"/>
-      <c r="AW4" s="399" t="s">
+      <c r="AT4" s="396"/>
+      <c r="AU4" s="396"/>
+      <c r="AV4" s="397"/>
+      <c r="AW4" s="395" t="s">
         <v>176</v>
       </c>
-      <c r="AX4" s="400"/>
-      <c r="AY4" s="400"/>
-      <c r="AZ4" s="400"/>
-      <c r="BA4" s="400"/>
-      <c r="BB4" s="400"/>
-      <c r="BC4" s="401"/>
-      <c r="BD4" s="394" t="s">
+      <c r="AX4" s="396"/>
+      <c r="AY4" s="396"/>
+      <c r="AZ4" s="396"/>
+      <c r="BA4" s="396"/>
+      <c r="BB4" s="396"/>
+      <c r="BC4" s="397"/>
+      <c r="BD4" s="398" t="s">
         <v>188</v>
       </c>
-      <c r="BE4" s="395"/>
-      <c r="BF4" s="395"/>
-      <c r="BG4" s="399" t="s">
+      <c r="BE4" s="399"/>
+      <c r="BF4" s="399"/>
+      <c r="BG4" s="395" t="s">
         <v>170</v>
       </c>
-      <c r="BH4" s="400"/>
-      <c r="BI4" s="400"/>
-      <c r="BJ4" s="401"/>
+      <c r="BH4" s="396"/>
+      <c r="BI4" s="396"/>
+      <c r="BJ4" s="397"/>
     </row>
     <row r="5" spans="2:72" x14ac:dyDescent="0.2">
       <c r="B5" s="358" t="s">
@@ -19910,7 +19910,7 @@
         <v>46122</v>
       </c>
       <c r="M5" s="362">
-        <f t="shared" ref="M5:AH5" si="1">L5+1</f>
+        <f t="shared" ref="M5:AG5" si="1">L5+1</f>
         <v>46123</v>
       </c>
       <c r="N5" s="362">
@@ -20045,7 +20045,7 @@
       <c r="AV5" s="70" t="s">
         <v>281</v>
       </c>
-      <c r="AW5" s="431" t="s">
+      <c r="AW5" s="393" t="s">
         <v>287</v>
       </c>
       <c r="AX5" s="364" t="s">
@@ -20167,38 +20167,32 @@
         <f>COUNTIFS(I6:AQ6,"HO*",$I$2:$AQ$2,"&lt;5",$I$1:$AQ$1,"")</f>
         <v>0</v>
       </c>
-      <c r="AX6" s="23">
-        <f>COUNTIFS(I6:AQ6,"HO*",$I$1:$AQ$1,"PRE")
- + COUNTIFS(I6:AQ6,"HO*",$I$2:$AQ$2,"5",$I$1:$AQ$1,"")
- - COUNTIFS(I6:AQ6,"HO6",$I$1:$AQ$1,"PRE")
- - COUNTIFS(I6:AQ6,"HO6",$I$2:$AQ$2,"5",$I$1:$AQ$1,"")</f>
-        <v>0</v>
-      </c>
-      <c r="AY6" s="23">
-        <f>COUNTIFS(I6:AQ6,"HO*",$I$1:$AQ$1,"Y")
- + COUNTIFS(I6:AQ6,"HO*",$I$2:$AQ$2,"6",$I$1:$AQ$1,"")
- - COUNTIFS(I6:AQ6,"HO6",$I$1:$AQ$1,"Y")
- - COUNTIFS(I6:AQ6,"HO6",$I$2:$AQ$2,"6",$I$1:$AQ$1,"")</f>
+      <c r="AX6" s="23" cm="1">
+        <f t="array" ref="AX6">SUMPRODUCT( (LEFT(I6:AQ6,2)="HO") * (I6:AQ6&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="23" cm="1">
+        <f t="array" ref="AY6">SUMPRODUCT( (LEFT(I6:AQ6,2)="HO") * (I6:AQ6&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
         <v>0</v>
       </c>
       <c r="AZ6" s="23">
-        <f>COUNTIFS(I6:AQ6,"HO*",$I$2:$AQ$2,"7",$I$1:$AQ$1,"") - COUNTIFS(I6:AQ6,"HO6",$I$2:$AQ$2,"7",$I$1:$AQ$1,"")</f>
+        <f t="shared" ref="AZ6" si="3">COUNTIFS(I6:AQ6,"HO*",$I$2:$AQ$2,"7",$I$1:$AQ$1,"") - COUNTIFS(I6:AQ6,"HO6",$I$2:$AQ$2,"7",$I$1:$AQ$1,"")</f>
         <v>0</v>
       </c>
       <c r="BA6" s="23">
-        <f t="shared" ref="BA6:BA45" si="3">COUNTIF(I6:AQ6,"HO6")</f>
+        <f t="shared" ref="BA6" si="4">COUNTIF(I6:AQ6,"HO6")</f>
         <v>0</v>
       </c>
       <c r="BB6" s="278">
-        <f t="shared" ref="BB6:BB45" si="4">COUNTIF(I6:AQ6,"WR*")</f>
+        <f t="shared" ref="BB6" si="5">COUNTIF(I6:AQ6,"WR*")</f>
         <v>0</v>
       </c>
       <c r="BC6" s="39">
-        <f t="shared" ref="BC6:BC45" si="5">COUNTIF(I6:AQ6,"SB")</f>
+        <f t="shared" ref="BC6" si="6">COUNTIF(I6:AQ6,"SB")</f>
         <v>0</v>
       </c>
       <c r="BD6" s="25">
-        <f t="shared" ref="BD6:BD45" si="6">SUM(AW6:AZ6)+BA6*0.5</f>
+        <f t="shared" ref="BD6:BD45" si="7">SUM(AW6:AZ6)+BA6*0.5</f>
         <v>0</v>
       </c>
       <c r="BE6" s="18">
@@ -20210,19 +20204,19 @@
         <v>5</v>
       </c>
       <c r="BG6" s="25">
-        <f t="shared" ref="BG6:BG45" si="7">BD6+AS6</f>
+        <f t="shared" ref="BG6:BG45" si="8">BD6+AS6</f>
         <v>0</v>
       </c>
       <c r="BH6" s="18">
-        <f t="shared" ref="BH6:BH45" si="8">BE6+AT6</f>
+        <f t="shared" ref="BH6:BH45" si="9">BE6+AT6</f>
         <v>0</v>
       </c>
       <c r="BI6" s="18">
-        <f t="shared" ref="BI6:BI45" si="9">IF(AV6&lt;&gt;"", AV6+1, "")</f>
+        <f t="shared" ref="BI6:BI45" si="10">IF(AV6&lt;&gt;"", AV6+1, "")</f>
         <v>1</v>
       </c>
       <c r="BJ6" s="26">
-        <f t="shared" ref="BJ6:BJ45" si="10">BH6/BI6</f>
+        <f t="shared" ref="BJ6:BJ45" si="11">BH6/BI6</f>
         <v>0</v>
       </c>
     </row>
@@ -20292,45 +20286,39 @@
         <v>0</v>
       </c>
       <c r="AW7" s="42">
-        <f t="shared" ref="AW7:AW45" si="11">COUNTIFS(I7:AQ7,"HO*",$I$2:$AQ$2,"&lt;5",$I$1:$AQ$1,"")</f>
-        <v>0</v>
-      </c>
-      <c r="AX7" s="23">
-        <f t="shared" ref="AX7:AX45" si="12">COUNTIFS(I7:AQ7,"HO*",$I$1:$AQ$1,"PRE")
- + COUNTIFS(I7:AQ7,"HO*",$I$2:$AQ$2,"5",$I$1:$AQ$1,"")
- - COUNTIFS(I7:AQ7,"HO6",$I$1:$AQ$1,"PRE")
- - COUNTIFS(I7:AQ7,"HO6",$I$2:$AQ$2,"5",$I$1:$AQ$1,"")</f>
-        <v>0</v>
-      </c>
-      <c r="AY7" s="23">
-        <f t="shared" ref="AY7:AY45" si="13">COUNTIFS(I7:AQ7,"HO*",$I$1:$AQ$1,"Y")
- + COUNTIFS(I7:AQ7,"HO*",$I$2:$AQ$2,"6",$I$1:$AQ$1,"")
- - COUNTIFS(I7:AQ7,"HO6",$I$1:$AQ$1,"Y")
- - COUNTIFS(I7:AQ7,"HO6",$I$2:$AQ$2,"6",$I$1:$AQ$1,"")</f>
+        <f t="shared" ref="AW7:AW45" si="12">COUNTIFS(I7:AQ7,"HO*",$I$2:$AQ$2,"&lt;5",$I$1:$AQ$1,"")</f>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="23" cm="1">
+        <f t="array" ref="AX7">SUMPRODUCT( (LEFT(I7:AQ7,2)="HO") * (I7:AQ7&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="23" cm="1">
+        <f t="array" ref="AY7">SUMPRODUCT( (LEFT(I7:AQ7,2)="HO") * (I7:AQ7&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
         <v>0</v>
       </c>
       <c r="AZ7" s="23">
-        <f t="shared" ref="AZ7:AZ45" si="14">COUNTIFS(I7:AQ7,"HO*",$I$2:$AQ$2,"7",$I$1:$AQ$1,"") - COUNTIFS(I7:AQ7,"HO6",$I$2:$AQ$2,"7",$I$1:$AQ$1,"")</f>
+        <f t="shared" ref="AZ7:AZ45" si="13">COUNTIFS(I7:AQ7,"HO*",$I$2:$AQ$2,"7",$I$1:$AQ$1,"") - COUNTIFS(I7:AQ7,"HO6",$I$2:$AQ$2,"7",$I$1:$AQ$1,"")</f>
         <v>0</v>
       </c>
       <c r="BA7" s="23">
-        <f t="shared" ref="BA7:BA45" si="15">COUNTIF(I7:AQ7,"HO6")</f>
+        <f t="shared" ref="BA7:BA45" si="14">COUNTIF(I7:AQ7,"HO6")</f>
         <v>0</v>
       </c>
       <c r="BB7" s="278">
-        <f t="shared" ref="BB7:BB45" si="16">COUNTIF(I7:AQ7,"WR*")</f>
+        <f t="shared" ref="BB7:BB45" si="15">COUNTIF(I7:AQ7,"WR*")</f>
         <v>0</v>
       </c>
       <c r="BC7" s="39">
-        <f t="shared" ref="BC7:BC45" si="17">COUNTIF(I7:AQ7,"SB")</f>
+        <f t="shared" ref="BC7:BC45" si="16">COUNTIF(I7:AQ7,"SB")</f>
         <v>0</v>
       </c>
       <c r="BD7" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BE7" s="18">
-        <f t="shared" ref="BE7:BE45" si="18">AW7*1+AX7*1.5+AY7*2.5+AZ7*2+BA7*0.5</f>
+        <f t="shared" ref="BE7:BE45" si="17">AW7*1+AX7*1.5+AY7*2.5+AZ7*2+BA7*0.5</f>
         <v>0</v>
       </c>
       <c r="BF7" s="346" cm="1">
@@ -20338,19 +20326,19 @@
         <v>5</v>
       </c>
       <c r="BG7" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH7" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI7" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ7" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -20420,39 +20408,39 @@
         <v>0</v>
       </c>
       <c r="AW8" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX8" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY8" s="23">
+      <c r="AX8" s="23" cm="1">
+        <f t="array" ref="AX8">SUMPRODUCT( (LEFT(I8:AQ8,2)="HO") * (I8:AQ8&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="23" cm="1">
+        <f t="array" ref="AY8">SUMPRODUCT( (LEFT(I8:AQ8,2)="HO") * (I8:AQ8&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ8" s="23">
+      <c r="BA8" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA8" s="23">
+      <c r="BB8" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB8" s="278">
+      <c r="BC8" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC8" s="39">
+      <c r="BD8" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE8" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD8" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE8" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF8" s="346" cm="1">
@@ -20460,19 +20448,19 @@
         <v>5</v>
       </c>
       <c r="BG8" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH8" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI8" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ8" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -20542,39 +20530,39 @@
         <v>0</v>
       </c>
       <c r="AW9" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX9" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY9" s="23">
+      <c r="AX9" s="23" cm="1">
+        <f t="array" ref="AX9">SUMPRODUCT( (LEFT(I9:AQ9,2)="HO") * (I9:AQ9&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY9" s="23" cm="1">
+        <f t="array" ref="AY9">SUMPRODUCT( (LEFT(I9:AQ9,2)="HO") * (I9:AQ9&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ9" s="23">
+      <c r="BA9" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA9" s="23">
+      <c r="BB9" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB9" s="278">
+      <c r="BC9" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC9" s="39">
+      <c r="BD9" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE9" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD9" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE9" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF9" s="346" cm="1">
@@ -20582,19 +20570,19 @@
         <v>5</v>
       </c>
       <c r="BG9" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH9" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI9" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ9" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -20664,39 +20652,39 @@
         <v>0</v>
       </c>
       <c r="AW10" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX10" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY10" s="23">
+      <c r="AX10" s="23" cm="1">
+        <f t="array" ref="AX10">SUMPRODUCT( (LEFT(I10:AQ10,2)="HO") * (I10:AQ10&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY10" s="23" cm="1">
+        <f t="array" ref="AY10">SUMPRODUCT( (LEFT(I10:AQ10,2)="HO") * (I10:AQ10&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ10" s="23">
+      <c r="BA10" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA10" s="23">
+      <c r="BB10" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB10" s="278">
+      <c r="BC10" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC10" s="39">
+      <c r="BD10" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE10" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD10" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE10" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF10" s="346" cm="1">
@@ -20704,19 +20692,19 @@
         <v>5</v>
       </c>
       <c r="BG10" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH10" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI10" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ10" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -20786,39 +20774,39 @@
         <v>0</v>
       </c>
       <c r="AW11" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX11" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY11" s="23">
+      <c r="AX11" s="23" cm="1">
+        <f t="array" ref="AX11">SUMPRODUCT( (LEFT(I11:AQ11,2)="HO") * (I11:AQ11&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY11" s="23" cm="1">
+        <f t="array" ref="AY11">SUMPRODUCT( (LEFT(I11:AQ11,2)="HO") * (I11:AQ11&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ11" s="23">
+      <c r="BA11" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA11" s="23">
+      <c r="BB11" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB11" s="278">
+      <c r="BC11" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC11" s="39">
+      <c r="BD11" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE11" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD11" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE11" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF11" s="346" cm="1">
@@ -20826,19 +20814,19 @@
         <v>5</v>
       </c>
       <c r="BG11" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH11" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI11" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ11" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -20908,39 +20896,39 @@
         <v>0</v>
       </c>
       <c r="AW12" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX12" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY12" s="23">
+      <c r="AX12" s="23" cm="1">
+        <f t="array" ref="AX12">SUMPRODUCT( (LEFT(I12:AQ12,2)="HO") * (I12:AQ12&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY12" s="23" cm="1">
+        <f t="array" ref="AY12">SUMPRODUCT( (LEFT(I12:AQ12,2)="HO") * (I12:AQ12&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ12" s="23">
+      <c r="BA12" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA12" s="23">
+      <c r="BB12" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB12" s="278">
+      <c r="BC12" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC12" s="39">
+      <c r="BD12" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE12" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD12" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE12" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF12" s="346" cm="1">
@@ -20948,19 +20936,19 @@
         <v>5</v>
       </c>
       <c r="BG12" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH12" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI12" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ12" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -21030,39 +21018,39 @@
         <v>0</v>
       </c>
       <c r="AW13" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX13" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY13" s="23">
+      <c r="AX13" s="23" cm="1">
+        <f t="array" ref="AX13">SUMPRODUCT( (LEFT(I13:AQ13,2)="HO") * (I13:AQ13&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY13" s="23" cm="1">
+        <f t="array" ref="AY13">SUMPRODUCT( (LEFT(I13:AQ13,2)="HO") * (I13:AQ13&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ13" s="23">
+      <c r="BA13" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA13" s="23">
+      <c r="BB13" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB13" s="278">
+      <c r="BC13" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC13" s="39">
+      <c r="BD13" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE13" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD13" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE13" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF13" s="346" cm="1">
@@ -21070,19 +21058,19 @@
         <v>5</v>
       </c>
       <c r="BG13" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH13" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI13" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ13" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -21152,39 +21140,39 @@
         <v>0</v>
       </c>
       <c r="AW14" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX14" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY14" s="23">
+      <c r="AX14" s="23" cm="1">
+        <f t="array" ref="AX14">SUMPRODUCT( (LEFT(I14:AQ14,2)="HO") * (I14:AQ14&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY14" s="23" cm="1">
+        <f t="array" ref="AY14">SUMPRODUCT( (LEFT(I14:AQ14,2)="HO") * (I14:AQ14&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ14" s="23">
+      <c r="BA14" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA14" s="23">
+      <c r="BB14" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB14" s="278">
+      <c r="BC14" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC14" s="39">
+      <c r="BD14" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE14" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD14" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE14" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF14" s="346" cm="1">
@@ -21192,19 +21180,19 @@
         <v>5</v>
       </c>
       <c r="BG14" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH14" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI14" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ14" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -21274,39 +21262,39 @@
         <v>0</v>
       </c>
       <c r="AW15" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX15" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY15" s="23">
+      <c r="AX15" s="23" cm="1">
+        <f t="array" ref="AX15">SUMPRODUCT( (LEFT(I15:AQ15,2)="HO") * (I15:AQ15&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY15" s="23" cm="1">
+        <f t="array" ref="AY15">SUMPRODUCT( (LEFT(I15:AQ15,2)="HO") * (I15:AQ15&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ15" s="23">
+      <c r="BA15" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA15" s="23">
+      <c r="BB15" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB15" s="278">
+      <c r="BC15" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC15" s="39">
+      <c r="BD15" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE15" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD15" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE15" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF15" s="346" cm="1">
@@ -21314,19 +21302,19 @@
         <v>5</v>
       </c>
       <c r="BG15" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH15" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI15" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ15" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -21396,39 +21384,39 @@
         <v>0</v>
       </c>
       <c r="AW16" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX16" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY16" s="23">
+      <c r="AX16" s="23" cm="1">
+        <f t="array" ref="AX16">SUMPRODUCT( (LEFT(I16:AQ16,2)="HO") * (I16:AQ16&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY16" s="23" cm="1">
+        <f t="array" ref="AY16">SUMPRODUCT( (LEFT(I16:AQ16,2)="HO") * (I16:AQ16&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ16" s="23">
+      <c r="BA16" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA16" s="23">
+      <c r="BB16" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB16" s="278">
+      <c r="BC16" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC16" s="39">
+      <c r="BD16" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE16" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD16" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE16" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF16" s="346" cm="1">
@@ -21436,19 +21424,19 @@
         <v>5</v>
       </c>
       <c r="BG16" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH16" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI16" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ16" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -21518,39 +21506,39 @@
         <v>0</v>
       </c>
       <c r="AW17" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX17" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY17" s="23">
+      <c r="AX17" s="23" cm="1">
+        <f t="array" ref="AX17">SUMPRODUCT( (LEFT(I17:AQ17,2)="HO") * (I17:AQ17&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY17" s="23" cm="1">
+        <f t="array" ref="AY17">SUMPRODUCT( (LEFT(I17:AQ17,2)="HO") * (I17:AQ17&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ17" s="23">
+      <c r="BA17" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA17" s="23">
+      <c r="BB17" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB17" s="278">
+      <c r="BC17" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC17" s="39">
+      <c r="BD17" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE17" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD17" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE17" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF17" s="346" cm="1">
@@ -21558,19 +21546,19 @@
         <v>5</v>
       </c>
       <c r="BG17" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH17" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI17" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ17" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -21640,39 +21628,39 @@
         <v>0</v>
       </c>
       <c r="AW18" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX18" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY18" s="23">
+      <c r="AX18" s="23" cm="1">
+        <f t="array" ref="AX18">SUMPRODUCT( (LEFT(I18:AQ18,2)="HO") * (I18:AQ18&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY18" s="23" cm="1">
+        <f t="array" ref="AY18">SUMPRODUCT( (LEFT(I18:AQ18,2)="HO") * (I18:AQ18&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ18" s="23">
+      <c r="BA18" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA18" s="23">
+      <c r="BB18" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB18" s="278">
+      <c r="BC18" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC18" s="39">
+      <c r="BD18" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE18" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE18" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF18" s="346" cm="1">
@@ -21680,19 +21668,19 @@
         <v>5</v>
       </c>
       <c r="BG18" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH18" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI18" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ18" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -21762,39 +21750,39 @@
         <v>0</v>
       </c>
       <c r="AW19" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX19" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY19" s="23">
+      <c r="AX19" s="23" cm="1">
+        <f t="array" ref="AX19">SUMPRODUCT( (LEFT(I19:AQ19,2)="HO") * (I19:AQ19&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY19" s="23" cm="1">
+        <f t="array" ref="AY19">SUMPRODUCT( (LEFT(I19:AQ19,2)="HO") * (I19:AQ19&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ19" s="23">
+      <c r="BA19" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA19" s="23">
+      <c r="BB19" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB19" s="278">
+      <c r="BC19" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC19" s="39">
+      <c r="BD19" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE19" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD19" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE19" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF19" s="346" cm="1">
@@ -21802,19 +21790,19 @@
         <v>5</v>
       </c>
       <c r="BG19" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH19" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI19" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ19" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -21884,39 +21872,39 @@
         <v>0</v>
       </c>
       <c r="AW20" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX20" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY20" s="23">
+      <c r="AX20" s="23" cm="1">
+        <f t="array" ref="AX20">SUMPRODUCT( (LEFT(I20:AQ20,2)="HO") * (I20:AQ20&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY20" s="23" cm="1">
+        <f t="array" ref="AY20">SUMPRODUCT( (LEFT(I20:AQ20,2)="HO") * (I20:AQ20&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ20" s="23">
+      <c r="BA20" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA20" s="23">
+      <c r="BB20" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB20" s="278">
+      <c r="BC20" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC20" s="39">
+      <c r="BD20" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE20" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD20" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE20" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF20" s="346" cm="1">
@@ -21924,19 +21912,19 @@
         <v>5</v>
       </c>
       <c r="BG20" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH20" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI20" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ20" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -22006,39 +21994,39 @@
         <v>0</v>
       </c>
       <c r="AW21" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX21" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY21" s="23">
+      <c r="AX21" s="23" cm="1">
+        <f t="array" ref="AX21">SUMPRODUCT( (LEFT(I21:AQ21,2)="HO") * (I21:AQ21&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY21" s="23" cm="1">
+        <f t="array" ref="AY21">SUMPRODUCT( (LEFT(I21:AQ21,2)="HO") * (I21:AQ21&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ21" s="23">
+      <c r="BA21" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA21" s="23">
+      <c r="BB21" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB21" s="278">
+      <c r="BC21" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC21" s="39">
+      <c r="BD21" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE21" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD21" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE21" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF21" s="346" cm="1">
@@ -22046,19 +22034,19 @@
         <v>5</v>
       </c>
       <c r="BG21" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH21" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI21" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ21" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -22128,39 +22116,39 @@
         <v>0</v>
       </c>
       <c r="AW22" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX22" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY22" s="23">
+      <c r="AX22" s="23" cm="1">
+        <f t="array" ref="AX22">SUMPRODUCT( (LEFT(I22:AQ22,2)="HO") * (I22:AQ22&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY22" s="23" cm="1">
+        <f t="array" ref="AY22">SUMPRODUCT( (LEFT(I22:AQ22,2)="HO") * (I22:AQ22&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ22" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ22" s="23">
+      <c r="BA22" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA22" s="23">
+      <c r="BB22" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB22" s="278">
+      <c r="BC22" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC22" s="39">
+      <c r="BD22" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE22" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD22" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE22" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF22" s="346" cm="1">
@@ -22168,19 +22156,19 @@
         <v>5</v>
       </c>
       <c r="BG22" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH22" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI22" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ22" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -22250,39 +22238,39 @@
         <v>0</v>
       </c>
       <c r="AW23" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX23" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY23" s="23">
+      <c r="AX23" s="23" cm="1">
+        <f t="array" ref="AX23">SUMPRODUCT( (LEFT(I23:AQ23,2)="HO") * (I23:AQ23&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY23" s="23" cm="1">
+        <f t="array" ref="AY23">SUMPRODUCT( (LEFT(I23:AQ23,2)="HO") * (I23:AQ23&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ23" s="23">
+      <c r="BA23" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA23" s="23">
+      <c r="BB23" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB23" s="278">
+      <c r="BC23" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC23" s="39">
+      <c r="BD23" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE23" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD23" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE23" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF23" s="346" cm="1">
@@ -22290,19 +22278,19 @@
         <v>5</v>
       </c>
       <c r="BG23" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH23" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI23" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ23" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -22372,39 +22360,39 @@
         <v>0</v>
       </c>
       <c r="AW24" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX24" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY24" s="23">
+      <c r="AX24" s="23" cm="1">
+        <f t="array" ref="AX24">SUMPRODUCT( (LEFT(I24:AQ24,2)="HO") * (I24:AQ24&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY24" s="23" cm="1">
+        <f t="array" ref="AY24">SUMPRODUCT( (LEFT(I24:AQ24,2)="HO") * (I24:AQ24&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ24" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ24" s="23">
+      <c r="BA24" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA24" s="23">
+      <c r="BB24" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB24" s="278">
+      <c r="BC24" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC24" s="39">
+      <c r="BD24" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE24" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD24" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE24" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF24" s="346" cm="1">
@@ -22412,19 +22400,19 @@
         <v>5</v>
       </c>
       <c r="BG24" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI24" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ24" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -22494,39 +22482,39 @@
         <v>0</v>
       </c>
       <c r="AW25" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX25" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY25" s="23">
+      <c r="AX25" s="23" cm="1">
+        <f t="array" ref="AX25">SUMPRODUCT( (LEFT(I25:AQ25,2)="HO") * (I25:AQ25&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="23" cm="1">
+        <f t="array" ref="AY25">SUMPRODUCT( (LEFT(I25:AQ25,2)="HO") * (I25:AQ25&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ25" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ25" s="23">
+      <c r="BA25" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA25" s="23">
+      <c r="BB25" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB25" s="278">
+      <c r="BC25" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC25" s="39">
+      <c r="BD25" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE25" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD25" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE25" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF25" s="346" cm="1">
@@ -22534,19 +22522,19 @@
         <v>5</v>
       </c>
       <c r="BG25" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH25" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI25" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ25" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -22616,39 +22604,39 @@
         <v>0</v>
       </c>
       <c r="AW26" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX26" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY26" s="23">
+      <c r="AX26" s="23" cm="1">
+        <f t="array" ref="AX26">SUMPRODUCT( (LEFT(I26:AQ26,2)="HO") * (I26:AQ26&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY26" s="23" cm="1">
+        <f t="array" ref="AY26">SUMPRODUCT( (LEFT(I26:AQ26,2)="HO") * (I26:AQ26&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ26" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ26" s="23">
+      <c r="BA26" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA26" s="23">
+      <c r="BB26" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB26" s="278">
+      <c r="BC26" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC26" s="39">
+      <c r="BD26" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE26" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD26" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE26" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF26" s="346" cm="1">
@@ -22656,19 +22644,19 @@
         <v>5</v>
       </c>
       <c r="BG26" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH26" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI26" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ26" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -22738,39 +22726,39 @@
         <v>0</v>
       </c>
       <c r="AW27" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX27" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY27" s="23">
+      <c r="AX27" s="23" cm="1">
+        <f t="array" ref="AX27">SUMPRODUCT( (LEFT(I27:AQ27,2)="HO") * (I27:AQ27&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY27" s="23" cm="1">
+        <f t="array" ref="AY27">SUMPRODUCT( (LEFT(I27:AQ27,2)="HO") * (I27:AQ27&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ27" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ27" s="23">
+      <c r="BA27" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA27" s="23">
+      <c r="BB27" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB27" s="278">
+      <c r="BC27" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC27" s="39">
+      <c r="BD27" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE27" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD27" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE27" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF27" s="346" cm="1">
@@ -22778,19 +22766,19 @@
         <v>5</v>
       </c>
       <c r="BG27" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH27" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI27" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ27" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -22860,39 +22848,39 @@
         <v>0</v>
       </c>
       <c r="AW28" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX28" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY28" s="23">
+      <c r="AX28" s="23" cm="1">
+        <f t="array" ref="AX28">SUMPRODUCT( (LEFT(I28:AQ28,2)="HO") * (I28:AQ28&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY28" s="23" cm="1">
+        <f t="array" ref="AY28">SUMPRODUCT( (LEFT(I28:AQ28,2)="HO") * (I28:AQ28&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ28" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ28" s="23">
+      <c r="BA28" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA28" s="23">
+      <c r="BB28" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB28" s="278">
+      <c r="BC28" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC28" s="39">
+      <c r="BD28" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE28" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD28" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE28" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF28" s="346" cm="1">
@@ -22900,19 +22888,19 @@
         <v>5</v>
       </c>
       <c r="BG28" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH28" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI28" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ28" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -22982,39 +22970,39 @@
         <v>0</v>
       </c>
       <c r="AW29" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX29" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY29" s="23">
+      <c r="AX29" s="23" cm="1">
+        <f t="array" ref="AX29">SUMPRODUCT( (LEFT(I29:AQ29,2)="HO") * (I29:AQ29&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY29" s="23" cm="1">
+        <f t="array" ref="AY29">SUMPRODUCT( (LEFT(I29:AQ29,2)="HO") * (I29:AQ29&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ29" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ29" s="23">
+      <c r="BA29" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA29" s="23">
+      <c r="BB29" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB29" s="278">
+      <c r="BC29" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC29" s="39">
+      <c r="BD29" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE29" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD29" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE29" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF29" s="346" cm="1">
@@ -23022,19 +23010,19 @@
         <v>5</v>
       </c>
       <c r="BG29" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH29" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI29" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ29" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -23104,39 +23092,39 @@
         <v>0</v>
       </c>
       <c r="AW30" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX30" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY30" s="23">
+      <c r="AX30" s="23" cm="1">
+        <f t="array" ref="AX30">SUMPRODUCT( (LEFT(I30:AQ30,2)="HO") * (I30:AQ30&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY30" s="23" cm="1">
+        <f t="array" ref="AY30">SUMPRODUCT( (LEFT(I30:AQ30,2)="HO") * (I30:AQ30&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ30" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ30" s="23">
+      <c r="BA30" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA30" s="23">
+      <c r="BB30" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB30" s="278">
+      <c r="BC30" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC30" s="39">
+      <c r="BD30" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE30" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD30" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE30" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF30" s="346" cm="1">
@@ -23144,19 +23132,19 @@
         <v>5</v>
       </c>
       <c r="BG30" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH30" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI30" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ30" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -23226,39 +23214,39 @@
         <v>0</v>
       </c>
       <c r="AW31" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX31" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY31" s="23">
+      <c r="AX31" s="23" cm="1">
+        <f t="array" ref="AX31">SUMPRODUCT( (LEFT(I31:AQ31,2)="HO") * (I31:AQ31&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY31" s="23" cm="1">
+        <f t="array" ref="AY31">SUMPRODUCT( (LEFT(I31:AQ31,2)="HO") * (I31:AQ31&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ31" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ31" s="23">
+      <c r="BA31" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA31" s="23">
+      <c r="BB31" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB31" s="278">
+      <c r="BC31" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC31" s="39">
+      <c r="BD31" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE31" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD31" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE31" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF31" s="346" cm="1">
@@ -23266,19 +23254,19 @@
         <v>5</v>
       </c>
       <c r="BG31" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH31" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI31" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ31" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -23348,39 +23336,39 @@
         <v>0</v>
       </c>
       <c r="AW32" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX32" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY32" s="23">
+      <c r="AX32" s="23" cm="1">
+        <f t="array" ref="AX32">SUMPRODUCT( (LEFT(I32:AQ32,2)="HO") * (I32:AQ32&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY32" s="23" cm="1">
+        <f t="array" ref="AY32">SUMPRODUCT( (LEFT(I32:AQ32,2)="HO") * (I32:AQ32&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ32" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ32" s="23">
+      <c r="BA32" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA32" s="23">
+      <c r="BB32" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB32" s="278">
+      <c r="BC32" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC32" s="39">
+      <c r="BD32" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE32" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD32" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE32" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF32" s="346" cm="1">
@@ -23388,19 +23376,19 @@
         <v>5</v>
       </c>
       <c r="BG32" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH32" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI32" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ32" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -23470,39 +23458,39 @@
         <v>0</v>
       </c>
       <c r="AW33" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX33" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY33" s="23">
+      <c r="AX33" s="23" cm="1">
+        <f t="array" ref="AX33">SUMPRODUCT( (LEFT(I33:AQ33,2)="HO") * (I33:AQ33&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY33" s="23" cm="1">
+        <f t="array" ref="AY33">SUMPRODUCT( (LEFT(I33:AQ33,2)="HO") * (I33:AQ33&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ33" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ33" s="23">
+      <c r="BA33" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA33" s="23">
+      <c r="BB33" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB33" s="278">
+      <c r="BC33" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC33" s="39">
+      <c r="BD33" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE33" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD33" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE33" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF33" s="346" cm="1">
@@ -23510,19 +23498,19 @@
         <v>5</v>
       </c>
       <c r="BG33" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH33" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI33" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ33" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -23592,39 +23580,39 @@
         <v>0</v>
       </c>
       <c r="AW34" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX34" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY34" s="23">
+      <c r="AX34" s="23" cm="1">
+        <f t="array" ref="AX34">SUMPRODUCT( (LEFT(I34:AQ34,2)="HO") * (I34:AQ34&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY34" s="23" cm="1">
+        <f t="array" ref="AY34">SUMPRODUCT( (LEFT(I34:AQ34,2)="HO") * (I34:AQ34&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ34" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ34" s="23">
+      <c r="BA34" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA34" s="23">
+      <c r="BB34" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB34" s="278">
+      <c r="BC34" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC34" s="39">
+      <c r="BD34" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE34" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD34" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE34" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF34" s="346" cm="1">
@@ -23632,19 +23620,19 @@
         <v>5</v>
       </c>
       <c r="BG34" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH34" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI34" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ34" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -23714,39 +23702,39 @@
         <v>0</v>
       </c>
       <c r="AW35" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX35" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY35" s="23">
+      <c r="AX35" s="23" cm="1">
+        <f t="array" ref="AX35">SUMPRODUCT( (LEFT(I35:AQ35,2)="HO") * (I35:AQ35&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY35" s="23" cm="1">
+        <f t="array" ref="AY35">SUMPRODUCT( (LEFT(I35:AQ35,2)="HO") * (I35:AQ35&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ35" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ35" s="23">
+      <c r="BA35" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA35" s="23">
+      <c r="BB35" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB35" s="278">
+      <c r="BC35" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC35" s="39">
+      <c r="BD35" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE35" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD35" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE35" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF35" s="346" cm="1">
@@ -23754,19 +23742,19 @@
         <v>5</v>
       </c>
       <c r="BG35" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH35" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI35" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ35" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -23836,39 +23824,39 @@
         <v>0</v>
       </c>
       <c r="AW36" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX36" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY36" s="23">
+      <c r="AX36" s="23" cm="1">
+        <f t="array" ref="AX36">SUMPRODUCT( (LEFT(I36:AQ36,2)="HO") * (I36:AQ36&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY36" s="23" cm="1">
+        <f t="array" ref="AY36">SUMPRODUCT( (LEFT(I36:AQ36,2)="HO") * (I36:AQ36&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ36" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ36" s="23">
+      <c r="BA36" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA36" s="23">
+      <c r="BB36" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB36" s="278">
+      <c r="BC36" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC36" s="39">
+      <c r="BD36" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE36" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD36" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE36" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF36" s="346" cm="1">
@@ -23876,19 +23864,19 @@
         <v>5</v>
       </c>
       <c r="BG36" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH36" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI36" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ36" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -23958,39 +23946,39 @@
         <v>0</v>
       </c>
       <c r="AW37" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX37" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY37" s="23">
+      <c r="AX37" s="23" cm="1">
+        <f t="array" ref="AX37">SUMPRODUCT( (LEFT(I37:AQ37,2)="HO") * (I37:AQ37&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY37" s="23" cm="1">
+        <f t="array" ref="AY37">SUMPRODUCT( (LEFT(I37:AQ37,2)="HO") * (I37:AQ37&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ37" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ37" s="23">
+      <c r="BA37" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA37" s="23">
+      <c r="BB37" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB37" s="278">
+      <c r="BC37" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC37" s="39">
+      <c r="BD37" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE37" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD37" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE37" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF37" s="346" cm="1">
@@ -23998,19 +23986,19 @@
         <v>5</v>
       </c>
       <c r="BG37" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH37" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI37" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ37" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -24080,39 +24068,39 @@
         <v>0</v>
       </c>
       <c r="AW38" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX38" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY38" s="23">
+      <c r="AX38" s="23" cm="1">
+        <f t="array" ref="AX38">SUMPRODUCT( (LEFT(I38:AQ38,2)="HO") * (I38:AQ38&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY38" s="23" cm="1">
+        <f t="array" ref="AY38">SUMPRODUCT( (LEFT(I38:AQ38,2)="HO") * (I38:AQ38&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ38" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ38" s="23">
+      <c r="BA38" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA38" s="23">
+      <c r="BB38" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB38" s="278">
+      <c r="BC38" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC38" s="39">
+      <c r="BD38" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE38" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD38" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE38" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF38" s="346" cm="1">
@@ -24120,19 +24108,19 @@
         <v>5</v>
       </c>
       <c r="BG38" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH38" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI38" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ38" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -24202,39 +24190,39 @@
         <v>0</v>
       </c>
       <c r="AW39" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX39" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY39" s="23">
+      <c r="AX39" s="23" cm="1">
+        <f t="array" ref="AX39">SUMPRODUCT( (LEFT(I39:AQ39,2)="HO") * (I39:AQ39&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY39" s="23" cm="1">
+        <f t="array" ref="AY39">SUMPRODUCT( (LEFT(I39:AQ39,2)="HO") * (I39:AQ39&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ39" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ39" s="23">
+      <c r="BA39" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA39" s="23">
+      <c r="BB39" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB39" s="278">
+      <c r="BC39" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC39" s="39">
+      <c r="BD39" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE39" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD39" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE39" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF39" s="346" cm="1">
@@ -24242,19 +24230,19 @@
         <v>5</v>
       </c>
       <c r="BG39" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH39" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI39" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ39" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -24324,39 +24312,39 @@
         <v>0</v>
       </c>
       <c r="AW40" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX40" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY40" s="23">
+      <c r="AX40" s="23" cm="1">
+        <f t="array" ref="AX40">SUMPRODUCT( (LEFT(I40:AQ40,2)="HO") * (I40:AQ40&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY40" s="23" cm="1">
+        <f t="array" ref="AY40">SUMPRODUCT( (LEFT(I40:AQ40,2)="HO") * (I40:AQ40&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ40" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ40" s="23">
+      <c r="BA40" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA40" s="23">
+      <c r="BB40" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB40" s="278">
+      <c r="BC40" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC40" s="39">
+      <c r="BD40" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE40" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD40" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE40" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF40" s="346" cm="1">
@@ -24364,19 +24352,19 @@
         <v>5</v>
       </c>
       <c r="BG40" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH40" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI40" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ40" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -24446,39 +24434,39 @@
         <v>0</v>
       </c>
       <c r="AW41" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX41" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY41" s="23">
+      <c r="AX41" s="23" cm="1">
+        <f t="array" ref="AX41">SUMPRODUCT( (LEFT(I41:AQ41,2)="HO") * (I41:AQ41&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY41" s="23" cm="1">
+        <f t="array" ref="AY41">SUMPRODUCT( (LEFT(I41:AQ41,2)="HO") * (I41:AQ41&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ41" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ41" s="23">
+      <c r="BA41" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA41" s="23">
+      <c r="BB41" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB41" s="278">
+      <c r="BC41" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC41" s="39">
+      <c r="BD41" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE41" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD41" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE41" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF41" s="346" cm="1">
@@ -24486,19 +24474,19 @@
         <v>5</v>
       </c>
       <c r="BG41" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH41" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI41" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ41" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -24568,39 +24556,39 @@
         <v>0</v>
       </c>
       <c r="AW42" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX42" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY42" s="23">
+      <c r="AX42" s="23" cm="1">
+        <f t="array" ref="AX42">SUMPRODUCT( (LEFT(I42:AQ42,2)="HO") * (I42:AQ42&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY42" s="23" cm="1">
+        <f t="array" ref="AY42">SUMPRODUCT( (LEFT(I42:AQ42,2)="HO") * (I42:AQ42&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ42" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ42" s="23">
+      <c r="BA42" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA42" s="23">
+      <c r="BB42" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB42" s="278">
+      <c r="BC42" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC42" s="39">
+      <c r="BD42" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE42" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD42" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE42" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF42" s="346" cm="1">
@@ -24608,19 +24596,19 @@
         <v>5</v>
       </c>
       <c r="BG42" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH42" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI42" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ42" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -24690,39 +24678,39 @@
         <v>0</v>
       </c>
       <c r="AW43" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX43" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY43" s="23">
+      <c r="AX43" s="23" cm="1">
+        <f t="array" ref="AX43">SUMPRODUCT( (LEFT(I43:AQ43,2)="HO") * (I43:AQ43&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY43" s="23" cm="1">
+        <f t="array" ref="AY43">SUMPRODUCT( (LEFT(I43:AQ43,2)="HO") * (I43:AQ43&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ43" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ43" s="23">
+      <c r="BA43" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA43" s="23">
+      <c r="BB43" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB43" s="278">
+      <c r="BC43" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC43" s="39">
+      <c r="BD43" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE43" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD43" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE43" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF43" s="346" cm="1">
@@ -24730,19 +24718,19 @@
         <v>5</v>
       </c>
       <c r="BG43" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH43" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI43" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ43" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -24812,39 +24800,39 @@
         <v>0</v>
       </c>
       <c r="AW44" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX44" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY44" s="23">
+      <c r="AX44" s="23" cm="1">
+        <f t="array" ref="AX44">SUMPRODUCT( (LEFT(I44:AQ44,2)="HO") * (I44:AQ44&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY44" s="23" cm="1">
+        <f t="array" ref="AY44">SUMPRODUCT( (LEFT(I44:AQ44,2)="HO") * (I44:AQ44&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ44" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ44" s="23">
+      <c r="BA44" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA44" s="23">
+      <c r="BB44" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB44" s="278">
+      <c r="BC44" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC44" s="39">
+      <c r="BD44" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE44" s="18">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD44" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE44" s="18">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF44" s="346" cm="1">
@@ -24852,19 +24840,19 @@
         <v>5</v>
       </c>
       <c r="BG44" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH44" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI44" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ44" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -24934,39 +24922,39 @@
         <v>0</v>
       </c>
       <c r="AW45" s="49">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AX45" s="48">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY45" s="48">
+      <c r="AX45" s="48" cm="1">
+        <f t="array" ref="AX45">SUMPRODUCT( (LEFT(I45:AQ45,2)="HO") * (I45:AQ45&lt;&gt;"HO6") * ( (($I$1:$AQ$1="PRE") + ($I$2:$AQ$2=5)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AY45" s="48" cm="1">
+        <f t="array" ref="AY45">SUMPRODUCT( (LEFT(I45:AQ45,2)="HO") * (I45:AQ45&lt;&gt;"HO6") * ( (($I$1:$AQ$1="Y") + ($I$2:$AQ$2=6)) &gt;0 ) )</f>
+        <v>0</v>
+      </c>
+      <c r="AZ45" s="48">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ45" s="48">
+      <c r="BA45" s="48">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA45" s="48">
+      <c r="BB45" s="279">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BB45" s="279">
+      <c r="BC45" s="50">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BC45" s="50">
+      <c r="BD45" s="33">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BE45" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BD45" s="33">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE45" s="34">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BF45" s="366" cm="1">
@@ -24974,19 +24962,19 @@
         <v>5</v>
       </c>
       <c r="BG45" s="33">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH45" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI45" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BJ45" s="41">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -24995,143 +24983,143 @@
         <v>30</v>
       </c>
       <c r="I47" s="1">
-        <f t="shared" ref="I47:I52" si="19">COUNTIFS(I$6:I$45,$D47)</f>
+        <f t="shared" ref="I47:I52" si="18">COUNTIFS(I$6:I$45,$D47)</f>
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <f t="shared" ref="J47:AQ52" si="20">COUNTIFS(J$6:J$45,$D47)</f>
+        <f t="shared" ref="J47:AQ52" si="19">COUNTIFS(J$6:J$45,$D47)</f>
         <v>0</v>
       </c>
       <c r="K47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="V47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="W47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="X47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Y47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AA47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AB47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AC47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AE47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AF47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AG47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AI47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AJ47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AK47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AL47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AM47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AN47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AO47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AP47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AQ47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -25140,143 +25128,143 @@
         <v>34</v>
       </c>
       <c r="I48" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
       <c r="K48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="V48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="W48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="X48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Y48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AA48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AB48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AC48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AE48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AF48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AG48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AI48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AJ48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AK48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AL48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AM48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AN48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AO48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AP48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AQ48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -25285,143 +25273,143 @@
         <v>32</v>
       </c>
       <c r="I49" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J49" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
       <c r="K49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="V49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="W49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="X49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Y49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AA49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AB49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AC49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AE49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AF49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AG49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AI49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AJ49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AK49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AL49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AM49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AN49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AO49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AP49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AQ49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -25430,143 +25418,143 @@
         <v>29</v>
       </c>
       <c r="I50" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J50" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
       <c r="K50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="V50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="W50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="X50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Y50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AA50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AB50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AC50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AE50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AF50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AG50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AI50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AJ50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AK50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AL50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AM50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AN50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AO50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AP50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AQ50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -25575,143 +25563,143 @@
         <v>31</v>
       </c>
       <c r="I51" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J51" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
       <c r="K51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="V51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="W51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="X51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Y51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AA51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AB51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AC51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AE51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AF51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AG51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AI51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AJ51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AK51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AL51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AM51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AN51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AO51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AP51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AQ51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -25720,143 +25708,143 @@
         <v>19</v>
       </c>
       <c r="I52" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J52" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
       <c r="K52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="V52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="W52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="X52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Y52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AA52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AB52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AC52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AE52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AF52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AG52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AI52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AJ52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AK52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AL52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AM52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AN52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AO52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AP52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AQ52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -25869,139 +25857,139 @@
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <f t="shared" ref="J53:AQ53" si="21">COUNTIFS(J$6:J$45,"WR*")</f>
+        <f t="shared" ref="J53:AQ53" si="20">COUNTIFS(J$6:J$45,"WR*")</f>
         <v>0</v>
       </c>
       <c r="K53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="N53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="O53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="P53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="T53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="U53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="X53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Y53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Z53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AA53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AB53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AC53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AD53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AE53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AG53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AH53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AI53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AK53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AL53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AM53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AN53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AO53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AP53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AQ53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -26014,139 +26002,139 @@
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <f t="shared" ref="J54:AQ54" si="22">COUNTIFS(J$6:J$45,"SB")</f>
+        <f t="shared" ref="J54:AQ54" si="21">COUNTIFS(J$6:J$45,"SB")</f>
         <v>0</v>
       </c>
       <c r="K54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="O54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="P54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="U54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="V54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="X54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Y54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Z54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AB54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AC54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AD54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AE54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AF54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AH54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AI54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AJ54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AL54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AM54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AN54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AO54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AP54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AQ54" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -26345,13 +26333,7 @@
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B83" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="C83" s="3"/>
-      <c r="D83" s="3">
-        <v>1</v>
-      </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
@@ -26775,28 +26757,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="402" t="s">
+      <c r="A1" s="403" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="403"/>
-      <c r="C1" s="408" t="s">
+      <c r="B1" s="404"/>
+      <c r="C1" s="409" t="s">
         <v>274</v>
       </c>
-      <c r="D1" s="409"/>
-      <c r="E1" s="409"/>
-      <c r="F1" s="409"/>
-      <c r="G1" s="409"/>
-      <c r="H1" s="409"/>
-      <c r="I1" s="409"/>
-      <c r="J1" s="409"/>
-      <c r="K1" s="409"/>
-      <c r="L1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
+      <c r="H1" s="410"/>
+      <c r="I1" s="410"/>
+      <c r="J1" s="410"/>
+      <c r="K1" s="410"/>
+      <c r="L1" s="411"/>
       <c r="M1" s="380"/>
       <c r="N1" s="380"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="404"/>
-      <c r="B2" s="405"/>
+      <c r="A2" s="405"/>
+      <c r="B2" s="406"/>
       <c r="C2" s="377" t="s">
         <v>30</v>
       </c>
@@ -26831,8 +26813,8 @@
       <c r="N2" s="380"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="406"/>
-      <c r="B3" s="407"/>
+      <c r="A3" s="407"/>
+      <c r="B3" s="408"/>
       <c r="C3" s="381" t="s">
         <v>275</v>
       </c>
@@ -28948,12 +28930,12 @@
       <c r="AH3" s="319" t="s">
         <v>160</v>
       </c>
-      <c r="AJ3" s="393" t="s">
+      <c r="AJ3" s="394" t="s">
         <v>120</v>
       </c>
-      <c r="AK3" s="393"/>
-      <c r="AL3" s="393"/>
-      <c r="AM3" s="393"/>
+      <c r="AK3" s="394"/>
+      <c r="AL3" s="394"/>
+      <c r="AM3" s="394"/>
     </row>
     <row r="4" spans="2:67" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F4" s="1" t="s">
@@ -28962,30 +28944,30 @@
       <c r="H4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AJ4" s="411" t="s">
+      <c r="AJ4" s="412" t="s">
         <v>133</v>
       </c>
-      <c r="AK4" s="412"/>
-      <c r="AL4" s="412"/>
-      <c r="AM4" s="413"/>
-      <c r="AN4" s="414" t="s">
+      <c r="AK4" s="413"/>
+      <c r="AL4" s="413"/>
+      <c r="AM4" s="414"/>
+      <c r="AN4" s="415" t="s">
         <v>175</v>
       </c>
-      <c r="AO4" s="415"/>
-      <c r="AP4" s="415"/>
-      <c r="AQ4" s="415"/>
-      <c r="AR4" s="415"/>
-      <c r="AS4" s="415"/>
-      <c r="AT4" s="415"/>
-      <c r="AU4" s="415"/>
-      <c r="AV4" s="415"/>
-      <c r="AW4" s="415"/>
-      <c r="AX4" s="415"/>
-      <c r="AY4" s="415"/>
-      <c r="AZ4" s="415"/>
-      <c r="BA4" s="415"/>
-      <c r="BB4" s="415"/>
-      <c r="BC4" s="416"/>
+      <c r="AO4" s="416"/>
+      <c r="AP4" s="416"/>
+      <c r="AQ4" s="416"/>
+      <c r="AR4" s="416"/>
+      <c r="AS4" s="416"/>
+      <c r="AT4" s="416"/>
+      <c r="AU4" s="416"/>
+      <c r="AV4" s="416"/>
+      <c r="AW4" s="416"/>
+      <c r="AX4" s="416"/>
+      <c r="AY4" s="416"/>
+      <c r="AZ4" s="416"/>
+      <c r="BA4" s="416"/>
+      <c r="BB4" s="416"/>
+      <c r="BC4" s="417"/>
     </row>
     <row r="5" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
@@ -29107,34 +29089,34 @@
         <v>46055</v>
       </c>
       <c r="AI5" s="5"/>
-      <c r="AJ5" s="417" t="s">
+      <c r="AJ5" s="418" t="s">
         <v>170</v>
       </c>
-      <c r="AK5" s="418"/>
-      <c r="AL5" s="418"/>
-      <c r="AM5" s="419"/>
-      <c r="AN5" s="423" t="s">
+      <c r="AK5" s="419"/>
+      <c r="AL5" s="419"/>
+      <c r="AM5" s="420"/>
+      <c r="AN5" s="424" t="s">
         <v>176</v>
       </c>
-      <c r="AO5" s="424"/>
-      <c r="AP5" s="424"/>
-      <c r="AQ5" s="424"/>
-      <c r="AR5" s="424"/>
-      <c r="AS5" s="425"/>
-      <c r="AT5" s="423" t="s">
+      <c r="AO5" s="425"/>
+      <c r="AP5" s="425"/>
+      <c r="AQ5" s="425"/>
+      <c r="AR5" s="425"/>
+      <c r="AS5" s="426"/>
+      <c r="AT5" s="424" t="s">
         <v>188</v>
       </c>
-      <c r="AU5" s="424"/>
-      <c r="AV5" s="424"/>
-      <c r="AW5" s="424"/>
-      <c r="AX5" s="425"/>
-      <c r="AY5" s="423" t="s">
+      <c r="AU5" s="425"/>
+      <c r="AV5" s="425"/>
+      <c r="AW5" s="425"/>
+      <c r="AX5" s="426"/>
+      <c r="AY5" s="424" t="s">
         <v>170</v>
       </c>
-      <c r="AZ5" s="424"/>
-      <c r="BA5" s="424"/>
-      <c r="BB5" s="424"/>
-      <c r="BC5" s="425"/>
+      <c r="AZ5" s="425"/>
+      <c r="BA5" s="425"/>
+      <c r="BB5" s="425"/>
+      <c r="BC5" s="426"/>
       <c r="BD5" s="5"/>
       <c r="BE5" s="5"/>
       <c r="BF5" s="5"/>
@@ -29268,26 +29250,26 @@
         <v>1</v>
       </c>
       <c r="AI6" s="5"/>
-      <c r="AJ6" s="420"/>
-      <c r="AK6" s="421"/>
-      <c r="AL6" s="421"/>
-      <c r="AM6" s="422"/>
-      <c r="AN6" s="426"/>
-      <c r="AO6" s="427"/>
-      <c r="AP6" s="427"/>
-      <c r="AQ6" s="427"/>
-      <c r="AR6" s="427"/>
-      <c r="AS6" s="428"/>
-      <c r="AT6" s="426"/>
-      <c r="AU6" s="427"/>
-      <c r="AV6" s="427"/>
-      <c r="AW6" s="427"/>
-      <c r="AX6" s="428"/>
-      <c r="AY6" s="426"/>
-      <c r="AZ6" s="427"/>
-      <c r="BA6" s="427"/>
-      <c r="BB6" s="427"/>
-      <c r="BC6" s="428"/>
+      <c r="AJ6" s="421"/>
+      <c r="AK6" s="422"/>
+      <c r="AL6" s="422"/>
+      <c r="AM6" s="423"/>
+      <c r="AN6" s="427"/>
+      <c r="AO6" s="428"/>
+      <c r="AP6" s="428"/>
+      <c r="AQ6" s="428"/>
+      <c r="AR6" s="428"/>
+      <c r="AS6" s="429"/>
+      <c r="AT6" s="427"/>
+      <c r="AU6" s="428"/>
+      <c r="AV6" s="428"/>
+      <c r="AW6" s="428"/>
+      <c r="AX6" s="429"/>
+      <c r="AY6" s="427"/>
+      <c r="AZ6" s="428"/>
+      <c r="BA6" s="428"/>
+      <c r="BB6" s="428"/>
+      <c r="BC6" s="429"/>
       <c r="BD6" s="5"/>
       <c r="BE6" s="5"/>
       <c r="BF6" s="5"/>
@@ -36512,12 +36494,12 @@
       <c r="AQ3" s="242" t="s">
         <v>160</v>
       </c>
-      <c r="AS3" s="429" t="s">
+      <c r="AS3" s="430" t="s">
         <v>120</v>
       </c>
-      <c r="AT3" s="429"/>
-      <c r="AU3" s="429"/>
-      <c r="AV3" s="429"/>
+      <c r="AT3" s="430"/>
+      <c r="AU3" s="430"/>
+      <c r="AV3" s="430"/>
     </row>
     <row r="4" spans="2:76" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F4" s="1" t="s">
@@ -36526,30 +36508,30 @@
       <c r="H4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AS4" s="411" t="s">
+      <c r="AS4" s="412" t="s">
         <v>133</v>
       </c>
-      <c r="AT4" s="412"/>
-      <c r="AU4" s="412"/>
-      <c r="AV4" s="413"/>
-      <c r="AW4" s="414" t="s">
+      <c r="AT4" s="413"/>
+      <c r="AU4" s="413"/>
+      <c r="AV4" s="414"/>
+      <c r="AW4" s="415" t="s">
         <v>175</v>
       </c>
-      <c r="AX4" s="415"/>
-      <c r="AY4" s="415"/>
-      <c r="AZ4" s="415"/>
-      <c r="BA4" s="415"/>
-      <c r="BB4" s="415"/>
-      <c r="BC4" s="415"/>
-      <c r="BD4" s="415"/>
-      <c r="BE4" s="415"/>
-      <c r="BF4" s="415"/>
-      <c r="BG4" s="415"/>
-      <c r="BH4" s="415"/>
-      <c r="BI4" s="415"/>
-      <c r="BJ4" s="415"/>
-      <c r="BK4" s="415"/>
-      <c r="BL4" s="416"/>
+      <c r="AX4" s="416"/>
+      <c r="AY4" s="416"/>
+      <c r="AZ4" s="416"/>
+      <c r="BA4" s="416"/>
+      <c r="BB4" s="416"/>
+      <c r="BC4" s="416"/>
+      <c r="BD4" s="416"/>
+      <c r="BE4" s="416"/>
+      <c r="BF4" s="416"/>
+      <c r="BG4" s="416"/>
+      <c r="BH4" s="416"/>
+      <c r="BI4" s="416"/>
+      <c r="BJ4" s="416"/>
+      <c r="BK4" s="416"/>
+      <c r="BL4" s="417"/>
     </row>
     <row r="5" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
@@ -36707,34 +36689,34 @@
         <v>46028</v>
       </c>
       <c r="AR5" s="5"/>
-      <c r="AS5" s="417" t="s">
+      <c r="AS5" s="418" t="s">
         <v>170</v>
       </c>
-      <c r="AT5" s="418"/>
-      <c r="AU5" s="418"/>
-      <c r="AV5" s="419"/>
-      <c r="AW5" s="423" t="s">
+      <c r="AT5" s="419"/>
+      <c r="AU5" s="419"/>
+      <c r="AV5" s="420"/>
+      <c r="AW5" s="424" t="s">
         <v>176</v>
       </c>
-      <c r="AX5" s="424"/>
-      <c r="AY5" s="424"/>
-      <c r="AZ5" s="424"/>
-      <c r="BA5" s="424"/>
-      <c r="BB5" s="425"/>
-      <c r="BC5" s="423" t="s">
+      <c r="AX5" s="425"/>
+      <c r="AY5" s="425"/>
+      <c r="AZ5" s="425"/>
+      <c r="BA5" s="425"/>
+      <c r="BB5" s="426"/>
+      <c r="BC5" s="424" t="s">
         <v>188</v>
       </c>
-      <c r="BD5" s="424"/>
-      <c r="BE5" s="424"/>
-      <c r="BF5" s="424"/>
-      <c r="BG5" s="425"/>
-      <c r="BH5" s="423" t="s">
+      <c r="BD5" s="425"/>
+      <c r="BE5" s="425"/>
+      <c r="BF5" s="425"/>
+      <c r="BG5" s="426"/>
+      <c r="BH5" s="424" t="s">
         <v>170</v>
       </c>
-      <c r="BI5" s="424"/>
-      <c r="BJ5" s="424"/>
-      <c r="BK5" s="424"/>
-      <c r="BL5" s="425"/>
+      <c r="BI5" s="425"/>
+      <c r="BJ5" s="425"/>
+      <c r="BK5" s="425"/>
+      <c r="BL5" s="426"/>
       <c r="BM5" s="5"/>
       <c r="BN5" s="5"/>
       <c r="BO5" s="5"/>
@@ -36902,26 +36884,26 @@
         <v>2</v>
       </c>
       <c r="AR6" s="5"/>
-      <c r="AS6" s="420"/>
-      <c r="AT6" s="421"/>
-      <c r="AU6" s="421"/>
-      <c r="AV6" s="422"/>
-      <c r="AW6" s="426"/>
-      <c r="AX6" s="427"/>
-      <c r="AY6" s="427"/>
-      <c r="AZ6" s="427"/>
-      <c r="BA6" s="427"/>
-      <c r="BB6" s="428"/>
-      <c r="BC6" s="426"/>
-      <c r="BD6" s="427"/>
-      <c r="BE6" s="427"/>
-      <c r="BF6" s="427"/>
-      <c r="BG6" s="428"/>
-      <c r="BH6" s="426"/>
-      <c r="BI6" s="427"/>
-      <c r="BJ6" s="427"/>
-      <c r="BK6" s="427"/>
-      <c r="BL6" s="428"/>
+      <c r="AS6" s="421"/>
+      <c r="AT6" s="422"/>
+      <c r="AU6" s="422"/>
+      <c r="AV6" s="423"/>
+      <c r="AW6" s="427"/>
+      <c r="AX6" s="428"/>
+      <c r="AY6" s="428"/>
+      <c r="AZ6" s="428"/>
+      <c r="BA6" s="428"/>
+      <c r="BB6" s="429"/>
+      <c r="BC6" s="427"/>
+      <c r="BD6" s="428"/>
+      <c r="BE6" s="428"/>
+      <c r="BF6" s="428"/>
+      <c r="BG6" s="429"/>
+      <c r="BH6" s="427"/>
+      <c r="BI6" s="428"/>
+      <c r="BJ6" s="428"/>
+      <c r="BK6" s="428"/>
+      <c r="BL6" s="429"/>
       <c r="BM6" s="5"/>
       <c r="BN6" s="5"/>
       <c r="BO6" s="5"/>
@@ -44731,12 +44713,12 @@
       <c r="AI3" s="242" t="s">
         <v>160</v>
       </c>
-      <c r="AK3" s="429" t="s">
+      <c r="AK3" s="430" t="s">
         <v>120</v>
       </c>
-      <c r="AL3" s="429"/>
-      <c r="AM3" s="429"/>
-      <c r="AN3" s="429"/>
+      <c r="AL3" s="430"/>
+      <c r="AM3" s="430"/>
+      <c r="AN3" s="430"/>
     </row>
     <row r="4" spans="2:68" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F4" s="1" t="s">
@@ -44745,30 +44727,30 @@
       <c r="H4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AK4" s="411" t="s">
+      <c r="AK4" s="412" t="s">
         <v>133</v>
       </c>
-      <c r="AL4" s="412"/>
-      <c r="AM4" s="412"/>
-      <c r="AN4" s="413"/>
-      <c r="AO4" s="414" t="s">
+      <c r="AL4" s="413"/>
+      <c r="AM4" s="413"/>
+      <c r="AN4" s="414"/>
+      <c r="AO4" s="415" t="s">
         <v>175</v>
       </c>
-      <c r="AP4" s="415"/>
-      <c r="AQ4" s="415"/>
-      <c r="AR4" s="415"/>
-      <c r="AS4" s="415"/>
-      <c r="AT4" s="415"/>
-      <c r="AU4" s="415"/>
-      <c r="AV4" s="415"/>
-      <c r="AW4" s="415"/>
-      <c r="AX4" s="415"/>
-      <c r="AY4" s="415"/>
-      <c r="AZ4" s="415"/>
-      <c r="BA4" s="415"/>
-      <c r="BB4" s="415"/>
-      <c r="BC4" s="415"/>
-      <c r="BD4" s="416"/>
+      <c r="AP4" s="416"/>
+      <c r="AQ4" s="416"/>
+      <c r="AR4" s="416"/>
+      <c r="AS4" s="416"/>
+      <c r="AT4" s="416"/>
+      <c r="AU4" s="416"/>
+      <c r="AV4" s="416"/>
+      <c r="AW4" s="416"/>
+      <c r="AX4" s="416"/>
+      <c r="AY4" s="416"/>
+      <c r="AZ4" s="416"/>
+      <c r="BA4" s="416"/>
+      <c r="BB4" s="416"/>
+      <c r="BC4" s="416"/>
+      <c r="BD4" s="417"/>
     </row>
     <row r="5" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
@@ -44894,34 +44876,34 @@
         <v>45992</v>
       </c>
       <c r="AJ5" s="5"/>
-      <c r="AK5" s="417" t="s">
+      <c r="AK5" s="418" t="s">
         <v>170</v>
       </c>
-      <c r="AL5" s="418"/>
-      <c r="AM5" s="418"/>
-      <c r="AN5" s="419"/>
-      <c r="AO5" s="423" t="s">
+      <c r="AL5" s="419"/>
+      <c r="AM5" s="419"/>
+      <c r="AN5" s="420"/>
+      <c r="AO5" s="424" t="s">
         <v>176</v>
       </c>
-      <c r="AP5" s="424"/>
-      <c r="AQ5" s="424"/>
-      <c r="AR5" s="424"/>
-      <c r="AS5" s="424"/>
-      <c r="AT5" s="425"/>
-      <c r="AU5" s="423" t="s">
+      <c r="AP5" s="425"/>
+      <c r="AQ5" s="425"/>
+      <c r="AR5" s="425"/>
+      <c r="AS5" s="425"/>
+      <c r="AT5" s="426"/>
+      <c r="AU5" s="424" t="s">
         <v>188</v>
       </c>
-      <c r="AV5" s="424"/>
-      <c r="AW5" s="424"/>
-      <c r="AX5" s="424"/>
-      <c r="AY5" s="425"/>
-      <c r="AZ5" s="423" t="s">
+      <c r="AV5" s="425"/>
+      <c r="AW5" s="425"/>
+      <c r="AX5" s="425"/>
+      <c r="AY5" s="426"/>
+      <c r="AZ5" s="424" t="s">
         <v>170</v>
       </c>
-      <c r="BA5" s="424"/>
-      <c r="BB5" s="424"/>
-      <c r="BC5" s="424"/>
-      <c r="BD5" s="425"/>
+      <c r="BA5" s="425"/>
+      <c r="BB5" s="425"/>
+      <c r="BC5" s="425"/>
+      <c r="BD5" s="426"/>
       <c r="BE5" s="5"/>
       <c r="BF5" s="5"/>
       <c r="BG5" s="5"/>
@@ -45061,26 +45043,26 @@
         <v>1</v>
       </c>
       <c r="AJ6" s="5"/>
-      <c r="AK6" s="420"/>
-      <c r="AL6" s="421"/>
-      <c r="AM6" s="421"/>
-      <c r="AN6" s="422"/>
-      <c r="AO6" s="426"/>
-      <c r="AP6" s="427"/>
-      <c r="AQ6" s="427"/>
-      <c r="AR6" s="427"/>
-      <c r="AS6" s="427"/>
-      <c r="AT6" s="428"/>
-      <c r="AU6" s="426"/>
-      <c r="AV6" s="427"/>
-      <c r="AW6" s="427"/>
-      <c r="AX6" s="427"/>
-      <c r="AY6" s="428"/>
-      <c r="AZ6" s="426"/>
-      <c r="BA6" s="427"/>
-      <c r="BB6" s="427"/>
-      <c r="BC6" s="427"/>
-      <c r="BD6" s="428"/>
+      <c r="AK6" s="421"/>
+      <c r="AL6" s="422"/>
+      <c r="AM6" s="422"/>
+      <c r="AN6" s="423"/>
+      <c r="AO6" s="427"/>
+      <c r="AP6" s="428"/>
+      <c r="AQ6" s="428"/>
+      <c r="AR6" s="428"/>
+      <c r="AS6" s="428"/>
+      <c r="AT6" s="429"/>
+      <c r="AU6" s="427"/>
+      <c r="AV6" s="428"/>
+      <c r="AW6" s="428"/>
+      <c r="AX6" s="428"/>
+      <c r="AY6" s="429"/>
+      <c r="AZ6" s="427"/>
+      <c r="BA6" s="428"/>
+      <c r="BB6" s="428"/>
+      <c r="BC6" s="428"/>
+      <c r="BD6" s="429"/>
       <c r="BE6" s="5"/>
       <c r="BF6" s="5"/>
       <c r="BG6" s="5"/>
@@ -52083,12 +52065,12 @@
       <c r="AH3" s="242" t="s">
         <v>160</v>
       </c>
-      <c r="AJ3" s="429" t="s">
+      <c r="AJ3" s="430" t="s">
         <v>120</v>
       </c>
-      <c r="AK3" s="429"/>
-      <c r="AL3" s="429"/>
-      <c r="AM3" s="429"/>
+      <c r="AK3" s="430"/>
+      <c r="AL3" s="430"/>
+      <c r="AM3" s="430"/>
     </row>
     <row r="4" spans="1:67" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E4" s="1" t="s">
@@ -52097,30 +52079,30 @@
       <c r="G4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AJ4" s="411" t="s">
+      <c r="AJ4" s="412" t="s">
         <v>133</v>
       </c>
-      <c r="AK4" s="412"/>
-      <c r="AL4" s="412"/>
-      <c r="AM4" s="413"/>
-      <c r="AN4" s="414" t="s">
+      <c r="AK4" s="413"/>
+      <c r="AL4" s="413"/>
+      <c r="AM4" s="414"/>
+      <c r="AN4" s="415" t="s">
         <v>175</v>
       </c>
-      <c r="AO4" s="415"/>
-      <c r="AP4" s="415"/>
-      <c r="AQ4" s="415"/>
-      <c r="AR4" s="415"/>
-      <c r="AS4" s="415"/>
-      <c r="AT4" s="415"/>
-      <c r="AU4" s="415"/>
-      <c r="AV4" s="415"/>
-      <c r="AW4" s="415"/>
-      <c r="AX4" s="415"/>
-      <c r="AY4" s="415"/>
-      <c r="AZ4" s="415"/>
-      <c r="BA4" s="415"/>
-      <c r="BB4" s="415"/>
-      <c r="BC4" s="416"/>
+      <c r="AO4" s="416"/>
+      <c r="AP4" s="416"/>
+      <c r="AQ4" s="416"/>
+      <c r="AR4" s="416"/>
+      <c r="AS4" s="416"/>
+      <c r="AT4" s="416"/>
+      <c r="AU4" s="416"/>
+      <c r="AV4" s="416"/>
+      <c r="AW4" s="416"/>
+      <c r="AX4" s="416"/>
+      <c r="AY4" s="416"/>
+      <c r="AZ4" s="416"/>
+      <c r="BA4" s="416"/>
+      <c r="BB4" s="416"/>
+      <c r="BC4" s="417"/>
     </row>
     <row r="5" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
@@ -52246,34 +52228,34 @@
         <v>45964</v>
       </c>
       <c r="AI5" s="5"/>
-      <c r="AJ5" s="417" t="s">
+      <c r="AJ5" s="418" t="s">
         <v>170</v>
       </c>
-      <c r="AK5" s="418"/>
-      <c r="AL5" s="418"/>
-      <c r="AM5" s="419"/>
-      <c r="AN5" s="423" t="s">
+      <c r="AK5" s="419"/>
+      <c r="AL5" s="419"/>
+      <c r="AM5" s="420"/>
+      <c r="AN5" s="424" t="s">
         <v>176</v>
       </c>
-      <c r="AO5" s="424"/>
-      <c r="AP5" s="424"/>
-      <c r="AQ5" s="424"/>
-      <c r="AR5" s="424"/>
-      <c r="AS5" s="425"/>
-      <c r="AT5" s="423" t="s">
+      <c r="AO5" s="425"/>
+      <c r="AP5" s="425"/>
+      <c r="AQ5" s="425"/>
+      <c r="AR5" s="425"/>
+      <c r="AS5" s="426"/>
+      <c r="AT5" s="424" t="s">
         <v>188</v>
       </c>
-      <c r="AU5" s="424"/>
-      <c r="AV5" s="424"/>
-      <c r="AW5" s="424"/>
-      <c r="AX5" s="425"/>
-      <c r="AY5" s="423" t="s">
+      <c r="AU5" s="425"/>
+      <c r="AV5" s="425"/>
+      <c r="AW5" s="425"/>
+      <c r="AX5" s="426"/>
+      <c r="AY5" s="424" t="s">
         <v>170</v>
       </c>
-      <c r="AZ5" s="424"/>
-      <c r="BA5" s="424"/>
-      <c r="BB5" s="424"/>
-      <c r="BC5" s="425"/>
+      <c r="AZ5" s="425"/>
+      <c r="BA5" s="425"/>
+      <c r="BB5" s="425"/>
+      <c r="BC5" s="426"/>
       <c r="BD5" s="5"/>
       <c r="BE5" s="5"/>
       <c r="BF5" s="5"/>
@@ -52411,26 +52393,26 @@
         <v>1</v>
       </c>
       <c r="AI6" s="5"/>
-      <c r="AJ6" s="420"/>
-      <c r="AK6" s="421"/>
-      <c r="AL6" s="421"/>
-      <c r="AM6" s="422"/>
-      <c r="AN6" s="426"/>
-      <c r="AO6" s="427"/>
-      <c r="AP6" s="427"/>
-      <c r="AQ6" s="427"/>
-      <c r="AR6" s="427"/>
-      <c r="AS6" s="428"/>
-      <c r="AT6" s="426"/>
-      <c r="AU6" s="427"/>
-      <c r="AV6" s="427"/>
-      <c r="AW6" s="427"/>
-      <c r="AX6" s="428"/>
-      <c r="AY6" s="426"/>
-      <c r="AZ6" s="427"/>
-      <c r="BA6" s="427"/>
-      <c r="BB6" s="427"/>
-      <c r="BC6" s="428"/>
+      <c r="AJ6" s="421"/>
+      <c r="AK6" s="422"/>
+      <c r="AL6" s="422"/>
+      <c r="AM6" s="423"/>
+      <c r="AN6" s="427"/>
+      <c r="AO6" s="428"/>
+      <c r="AP6" s="428"/>
+      <c r="AQ6" s="428"/>
+      <c r="AR6" s="428"/>
+      <c r="AS6" s="429"/>
+      <c r="AT6" s="427"/>
+      <c r="AU6" s="428"/>
+      <c r="AV6" s="428"/>
+      <c r="AW6" s="428"/>
+      <c r="AX6" s="429"/>
+      <c r="AY6" s="427"/>
+      <c r="AZ6" s="428"/>
+      <c r="BA6" s="428"/>
+      <c r="BB6" s="428"/>
+      <c r="BC6" s="429"/>
       <c r="BD6" s="5"/>
       <c r="BE6" s="5"/>
       <c r="BF6" s="5"/>
